--- a/reports/latest/Failed_Test_Cases.xlsx
+++ b/reports/latest/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Test ID</t>
   </si>
@@ -29,71 +29,6 @@
   </si>
   <si>
     <t>Screenshot File</t>
-  </si>
-  <si>
-    <t>TC_CRUD_024</t>
-  </si>
-  <si>
-    <t>CRUD Operations</t>
-  </si>
-  <si>
-    <t>Verify CRUD Operations Mobile Scenario 24 - Boundary Condition</t>
-  </si>
-  <si>
-    <t>Automated verification failed in CRUD Operations step 24: Validation message missing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AssertionError: Expected element to be visible on screen
-    at BasePage.waitForElement (automation/pages/BasePage.js:15:11)
-    at processTicksAndRejections (node:internal/process/task_queues:95:5)</t>
-  </si>
-  <si>
-    <t>TC_CRUD_024_failure.png</t>
-  </si>
-  <si>
-    <t>TC_VAL_008</t>
-  </si>
-  <si>
-    <t>Input Validation</t>
-  </si>
-  <si>
-    <t>Verify Input Validation Mobile Scenario 8 - Core Path</t>
-  </si>
-  <si>
-    <t>Automated verification failed in Input Validation step 8: Validation message missing.</t>
-  </si>
-  <si>
-    <t>TC_VAL_008_failure.png</t>
-  </si>
-  <si>
-    <t>TC_ERR_015</t>
-  </si>
-  <si>
-    <t>Error Handling</t>
-  </si>
-  <si>
-    <t>Verify Error Handling Mobile Scenario 15 - Boundary Condition</t>
-  </si>
-  <si>
-    <t>Automated verification failed in Error Handling step 15: Validation message missing.</t>
-  </si>
-  <si>
-    <t>TC_ERR_015_failure.png</t>
-  </si>
-  <si>
-    <t>TC_FILE_002</t>
-  </si>
-  <si>
-    <t>File Upload</t>
-  </si>
-  <si>
-    <t>Verify File Upload Mobile Scenario 2 - Core Path</t>
-  </si>
-  <si>
-    <t>Automated verification failed in File Upload step 2: Validation message missing.</t>
-  </si>
-  <si>
-    <t>TC_FILE_002_failure.png</t>
   </si>
 </sst>
 </file>
@@ -483,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -514,86 +449,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
